--- a/Homework2/my-simulation/question9.xlsx
+++ b/Homework2/my-simulation/question9.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Document_forme\project_tiny\Cource_report\DTUD\Homework2\my-simulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EE93404-B4BD-4FE2-B974-A0AF5CC5291F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9A8538-5364-4B1F-8CB6-8193FF6D166D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F11CDC6A-F5E9-4EBC-949A-D08DA2F43347}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>X--Trace 1::[I(R2)]</t>
   </si>
@@ -50,17 +50,52 @@
     <t>Delta I</t>
   </si>
   <si>
-    <t>Max Delta I</t>
+    <t>Error_input</t>
   </si>
   <si>
-    <t>Min Delta I</t>
+    <t>Error_output</t>
+  </si>
+  <si>
+    <t>Max Error Input</t>
+  </si>
+  <si>
+    <t>Min Error Input</t>
+  </si>
+  <si>
+    <t>Max Error Output</t>
+  </si>
+  <si>
+    <t>Min Error Output</t>
+  </si>
+  <si>
+    <t>MAX Delta V</t>
+  </si>
+  <si>
+    <t>MIN Delta V</t>
+  </si>
+  <si>
+    <t>MAX V_o</t>
+  </si>
+  <si>
+    <t>MIN V_o</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000000%"/>
+    <numFmt numFmtId="165" formatCode="0.00000%"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,14 +121,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -425,18 +464,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854BC47B-0D8A-445D-BEE8-8ED08B0F78CB}">
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -449,8 +489,14 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.04</v>
       </c>
@@ -465,15 +511,23 @@
         <f>B2-C2</f>
         <v>5.212711219392506E-6</v>
       </c>
-      <c r="F2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2">
-        <f>MAX($D:$D)</f>
-        <v>5.3723502475774843E-6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E2" s="1">
+        <f>(B2/100)/A2</f>
+        <v>1.0013031778048481E-3</v>
+      </c>
+      <c r="F2" s="1">
+        <f>D2/C2</f>
+        <v>1.3031778048481265E-3</v>
+      </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="2">
+        <f>MAX($E:$E)</f>
+        <v>1.0013031778048481E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>4.1599999999999998E-2</v>
       </c>
@@ -488,15 +542,23 @@
         <f t="shared" ref="D3:D66" si="1">B3-C3</f>
         <v>5.2193972622793794E-6</v>
       </c>
-      <c r="F3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <f>MIN($D:$D)</f>
-        <v>5.212711219392506E-6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E3" s="1">
+        <f t="shared" ref="E3:E66" si="2">(B3/100)/A3</f>
+        <v>1.0012546628034324E-3</v>
+      </c>
+      <c r="F3" s="1">
+        <f t="shared" ref="F3:F66" si="3">IF(C3=0, D3, D3/C3)</f>
+        <v>1.2546628034325433E-3</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="2">
+        <f>MIN($E:$E)</f>
+        <v>1.0002707689284935E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4.3199999999999995E-2</v>
       </c>
@@ -511,8 +573,16 @@
         <f t="shared" si="1"/>
         <v>5.2257407968346603E-6</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E4" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0012096622214895E-3</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" si="3"/>
+        <v>1.2096622214895047E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4.4799999999999993E-2</v>
       </c>
@@ -527,8 +597,23 @@
         <f t="shared" si="1"/>
         <v>5.2320581675141878E-6</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E5" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0011678701266774E-3</v>
+      </c>
+      <c r="F5" s="1">
+        <f t="shared" si="3"/>
+        <v>1.1678701266772742E-3</v>
+      </c>
+      <c r="G5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="2">
+        <f>MAX($F:$F)</f>
+        <v>1.3031778048481265E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4.639999999999999E-2</v>
       </c>
@@ -543,8 +628,23 @@
         <f t="shared" si="1"/>
         <v>5.237674605142531E-6</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E6" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0011288091821429E-3</v>
+      </c>
+      <c r="F6" s="1">
+        <f>IF(C6=0, D6, D6/C6)</f>
+        <v>1.1288091821427871E-3</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="2">
+        <f>MIN($F:$F)</f>
+        <v>2.7076892849350594E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4.7999999999999987E-2</v>
       </c>
@@ -559,8 +659,16 @@
         <f t="shared" si="1"/>
         <v>5.2432892401615971E-6</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E7" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0010923519250337E-3</v>
+      </c>
+      <c r="F7" s="1">
+        <f t="shared" si="3"/>
+        <v>1.0923519250336663E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4.9599999999999984E-2</v>
       </c>
@@ -575,8 +683,23 @@
         <f t="shared" si="1"/>
         <v>5.2481473044492521E-6</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E8" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0010580942146068E-3</v>
+      </c>
+      <c r="F8" s="1">
+        <f t="shared" si="3"/>
+        <v>1.0580942146067042E-3</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <f>MAX(D2:D202)</f>
+        <v>5.3723502475774843E-6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5.1199999999999982E-2</v>
       </c>
@@ -591,8 +714,23 @@
         <f t="shared" si="1"/>
         <v>5.2526949779075488E-6</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E9" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0010259169878726E-3</v>
+      </c>
+      <c r="F9" s="1">
+        <f t="shared" si="3"/>
+        <v>1.0259169878725685E-3</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9">
+        <f>MIN(D2:D202)</f>
+        <v>5.212711219392506E-6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>5.2799999999999979E-2</v>
       </c>
@@ -607,8 +745,16 @@
         <f t="shared" si="1"/>
         <v>5.2573287631588889E-6</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E10" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0009957062051438E-3</v>
+      </c>
+      <c r="F10" s="1">
+        <f t="shared" si="3"/>
+        <v>9.9570620514372933E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>5.4399999999999976E-2</v>
       </c>
@@ -623,8 +769,23 @@
         <f t="shared" si="1"/>
         <v>5.261847485330505E-6</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E11" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0009672513759799E-3</v>
+      </c>
+      <c r="F11" s="1">
+        <f t="shared" si="3"/>
+        <v>9.6725137597987259E-4</v>
+      </c>
+      <c r="G11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11">
+        <f>MAX($B$2:$B$202)</f>
+        <v>1.984537205554128E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>5.5999999999999973E-2</v>
       </c>
@@ -639,8 +800,23 @@
         <f t="shared" si="1"/>
         <v>5.2655553790291812E-6</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E12" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0009402777462553E-3</v>
+      </c>
+      <c r="F12" s="1">
+        <f t="shared" si="3"/>
+        <v>9.4027774625521138E-4</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <f>MIN($B$2:$B$202)</f>
+        <v>4.0052127112193926E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>5.7599999999999971E-2</v>
       </c>
@@ -655,8 +831,16 @@
         <f t="shared" si="1"/>
         <v>5.2695971316917695E-6</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E13" s="1">
+        <f t="shared" si="2"/>
+        <v>1.000914860613141E-3</v>
+      </c>
+      <c r="F13" s="1">
+        <f t="shared" si="3"/>
+        <v>9.1486061314093254E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>5.9199999999999968E-2</v>
       </c>
@@ -671,8 +855,16 @@
         <f t="shared" si="1"/>
         <v>5.2732407240302023E-6</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E14" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0008907501223025E-3</v>
+      </c>
+      <c r="F14" s="1">
+        <f t="shared" si="3"/>
+        <v>8.9075012230239948E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>6.0799999999999965E-2</v>
       </c>
@@ -687,8 +879,16 @@
         <f t="shared" si="1"/>
         <v>5.2771403938212808E-6</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E15" s="1">
+        <f t="shared" si="2"/>
+        <v>1.000867950722668E-3</v>
+      </c>
+      <c r="F15" s="1">
+        <f t="shared" si="3"/>
+        <v>8.6795072266797422E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>6.2399999999999962E-2</v>
       </c>
@@ -703,8 +903,16 @@
         <f t="shared" si="1"/>
         <v>5.2808076210575719E-6</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0008462832726054E-3</v>
+      </c>
+      <c r="F16" s="1">
+        <f t="shared" si="3"/>
+        <v>8.4628327260538063E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>6.399999999999996E-2</v>
       </c>
@@ -719,8 +927,16 @@
         <f t="shared" si="1"/>
         <v>5.2835453243534058E-6</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0008255539569301E-3</v>
+      </c>
+      <c r="F17" s="1">
+        <f t="shared" si="3"/>
+        <v>8.2555395693022021E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>6.5599999999999964E-2</v>
       </c>
@@ -735,8 +951,16 @@
         <f t="shared" si="1"/>
         <v>5.2861669013392829E-6</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0008058181252041E-3</v>
+      </c>
+      <c r="F18" s="1">
+        <f t="shared" si="3"/>
+        <v>8.0581812520415946E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>6.7199999999999968E-2</v>
       </c>
@@ -751,8 +975,16 @@
         <f t="shared" si="1"/>
         <v>5.289010904867622E-6</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0007870551941766E-3</v>
+      </c>
+      <c r="F19" s="1">
+        <f t="shared" si="3"/>
+        <v>7.8705519417672986E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>6.8799999999999972E-2</v>
       </c>
@@ -767,8 +999,16 @@
         <f t="shared" si="1"/>
         <v>5.2923315251064695E-6</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0007692342333004E-3</v>
+      </c>
+      <c r="F20" s="1">
+        <f t="shared" si="3"/>
+        <v>7.6923423330035922E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>7.0399999999999976E-2</v>
       </c>
@@ -783,8 +1023,16 @@
         <f t="shared" si="1"/>
         <v>5.2943448115728292E-6</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0007520376152802E-3</v>
+      </c>
+      <c r="F21" s="1">
+        <f t="shared" si="3"/>
+        <v>7.5203761528023171E-4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>7.1999999999999981E-2</v>
       </c>
@@ -799,8 +1047,16 @@
         <f t="shared" si="1"/>
         <v>5.2970456238983499E-6</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" s="1">
+        <f t="shared" si="2"/>
+        <v>1.000735700781097E-3</v>
+      </c>
+      <c r="F22" s="1">
+        <f t="shared" si="3"/>
+        <v>7.3570078109699323E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>7.3599999999999985E-2</v>
       </c>
@@ -815,8 +1071,16 @@
         <f t="shared" si="1"/>
         <v>5.3000542949406884E-6</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0007201160726821E-3</v>
+      </c>
+      <c r="F23" s="1">
+        <f t="shared" si="3"/>
+        <v>7.2011607268215893E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>7.5199999999999989E-2</v>
       </c>
@@ -831,8 +1095,16 @@
         <f t="shared" si="1"/>
         <v>5.3016690929278548E-6</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0007050091878893E-3</v>
+      </c>
+      <c r="F24" s="1">
+        <f t="shared" si="3"/>
+        <v>7.0500918788934247E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>7.6799999999999993E-2</v>
       </c>
@@ -847,8 +1119,16 @@
         <f t="shared" si="1"/>
         <v>5.3036257747600402E-6</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0006905762727553E-3</v>
+      </c>
+      <c r="F25" s="1">
+        <f t="shared" si="3"/>
+        <v>6.9057627275521363E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>7.8399999999999997E-2</v>
       </c>
@@ -863,8 +1143,16 @@
         <f t="shared" si="1"/>
         <v>5.3062549059471054E-6</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0006768182277994E-3</v>
+      </c>
+      <c r="F26" s="1">
+        <f t="shared" si="3"/>
+        <v>6.7681822779937575E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>0.08</v>
       </c>
@@ -879,8 +1167,16 @@
         <f t="shared" si="1"/>
         <v>5.3081491420397392E-6</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="1">
+        <f t="shared" si="2"/>
+        <v>1.000663518642755E-3</v>
+      </c>
+      <c r="F27" s="1">
+        <f t="shared" si="3"/>
+        <v>6.635186427549674E-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>8.1600000000000006E-2</v>
       </c>
@@ -895,8 +1191,16 @@
         <f t="shared" si="1"/>
         <v>5.3095381751470244E-6</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0006506786979347E-3</v>
+      </c>
+      <c r="F28" s="1">
+        <f t="shared" si="3"/>
+        <v>6.5067869793468435E-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>8.320000000000001E-2</v>
       </c>
@@ -911,8 +1215,16 @@
         <f t="shared" si="1"/>
         <v>5.3111534094128082E-6</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0006383597847852E-3</v>
+      </c>
+      <c r="F29" s="1">
+        <f t="shared" si="3"/>
+        <v>6.3835978478519323E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>8.4800000000000014E-2</v>
       </c>
@@ -927,8 +1239,16 @@
         <f t="shared" si="1"/>
         <v>5.3137137261492079E-6</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0006266171846874E-3</v>
+      </c>
+      <c r="F30" s="1">
+        <f t="shared" si="3"/>
+        <v>6.2661718468740653E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>8.6400000000000018E-2</v>
       </c>
@@ -943,8 +1263,16 @@
         <f t="shared" si="1"/>
         <v>5.3148835789107451E-6</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" s="1">
+        <f t="shared" si="2"/>
+        <v>1.000615148562374E-3</v>
+      </c>
+      <c r="F31" s="1">
+        <f t="shared" si="3"/>
+        <v>6.1514856237392872E-4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>8.8000000000000023E-2</v>
       </c>
@@ -959,8 +1287,16 @@
         <f t="shared" si="1"/>
         <v>5.3167171419604004E-6</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0006041724024955E-3</v>
+      </c>
+      <c r="F32" s="1">
+        <f t="shared" si="3"/>
+        <v>6.0417240249549986E-4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>8.9600000000000027E-2</v>
       </c>
@@ -975,8 +1311,16 @@
         <f t="shared" si="1"/>
         <v>5.3181114808825009E-6</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0005935392277769E-3</v>
+      </c>
+      <c r="F33" s="1">
+        <f t="shared" si="3"/>
+        <v>5.935392277770647E-4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9.1200000000000031E-2</v>
       </c>
@@ -991,8 +1335,16 @@
         <f t="shared" si="1"/>
         <v>5.3198040606029784E-6</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0005833118487504E-3</v>
+      </c>
+      <c r="F34" s="1">
+        <f t="shared" si="3"/>
+        <v>5.8331184875032641E-4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9.2800000000000035E-2</v>
       </c>
@@ -1007,8 +1359,16 @@
         <f t="shared" si="1"/>
         <v>5.3212534912271126E-6</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0005734109365546E-3</v>
+      </c>
+      <c r="F35" s="1">
+        <f t="shared" si="3"/>
+        <v>5.7341093655464558E-4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9.4400000000000039E-2</v>
       </c>
@@ -1023,8 +1383,16 @@
         <f t="shared" si="1"/>
         <v>5.3221416628015938E-6</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0005637861930934E-3</v>
+      </c>
+      <c r="F36" s="1">
+        <f t="shared" si="3"/>
+        <v>5.6378619309338897E-4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>9.6000000000000044E-2</v>
       </c>
@@ -1039,8 +1407,16 @@
         <f t="shared" si="1"/>
         <v>5.3244748689663252E-6</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0005546327988507E-3</v>
+      </c>
+      <c r="F37" s="1">
+        <f t="shared" si="3"/>
+        <v>5.5463279885065858E-4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>9.7600000000000048E-2</v>
       </c>
@@ -1055,8 +1431,16 @@
         <f t="shared" si="1"/>
         <v>5.3247022931274257E-6</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0005455637595417E-3</v>
+      </c>
+      <c r="F38" s="1">
+        <f t="shared" si="3"/>
+        <v>5.4556375954174416E-4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>9.9200000000000052E-2</v>
       </c>
@@ -1071,8 +1455,16 @@
         <f t="shared" si="1"/>
         <v>5.3264218922727952E-6</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0005369376907532E-3</v>
+      </c>
+      <c r="F39" s="1">
+        <f t="shared" si="3"/>
+        <v>5.3693769075330571E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>0.10080000000000006</v>
       </c>
@@ -1087,8 +1479,16 @@
         <f t="shared" si="1"/>
         <v>5.3272723322863452E-6</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E40" s="1">
+        <f t="shared" si="2"/>
+        <v>1.000528499239314E-3</v>
+      </c>
+      <c r="F40" s="1">
+        <f t="shared" si="3"/>
+        <v>5.2849923931412124E-4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>0.10240000000000006</v>
       </c>
@@ -1103,8 +1503,16 @@
         <f t="shared" si="1"/>
         <v>5.3281706162144893E-6</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E41" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0005203291617397E-3</v>
+      </c>
+      <c r="F41" s="1">
+        <f t="shared" si="3"/>
+        <v>5.2032916173969589E-4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>0.10400000000000006</v>
       </c>
@@ -1119,8 +1527,16 @@
         <f t="shared" si="1"/>
         <v>5.3302873193918077E-6</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E42" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0005125276268646E-3</v>
+      </c>
+      <c r="F42" s="1">
+        <f t="shared" si="3"/>
+        <v>5.1252762686459662E-4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>0.10560000000000007</v>
       </c>
@@ -1135,8 +1551,16 @@
         <f t="shared" si="1"/>
         <v>5.3304491789071817E-6</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E43" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0005047773843662E-3</v>
+      </c>
+      <c r="F43" s="1">
+        <f t="shared" si="3"/>
+        <v>5.0477738436621007E-4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>0.10720000000000007</v>
       </c>
@@ -1151,8 +1575,16 @@
         <f t="shared" si="1"/>
         <v>5.3318183261871072E-6</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0004973711125176E-3</v>
+      </c>
+      <c r="F44" s="1">
+        <f t="shared" si="3"/>
+        <v>4.9737111251745372E-4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>0.10880000000000008</v>
       </c>
@@ -1167,8 +1599,16 @@
         <f t="shared" si="1"/>
         <v>5.3332458314226533E-6</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E45" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0004901880359763E-3</v>
+      </c>
+      <c r="F45" s="1">
+        <f t="shared" si="3"/>
+        <v>4.9018803597634648E-4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>0.11040000000000008</v>
       </c>
@@ -1183,8 +1623,16 @@
         <f t="shared" si="1"/>
         <v>5.3345188596662374E-6</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E46" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0004831991720713E-3</v>
+      </c>
+      <c r="F46" s="1">
+        <f t="shared" si="3"/>
+        <v>4.8319917207121678E-4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>0.11200000000000009</v>
       </c>
@@ -1199,8 +1647,16 @@
         <f t="shared" si="1"/>
         <v>5.334518167546265E-6</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E47" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0004762962649595E-3</v>
+      </c>
+      <c r="F47" s="1">
+        <f t="shared" si="3"/>
+        <v>4.7629626495948759E-4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>0.11360000000000009</v>
       </c>
@@ -1215,8 +1671,16 @@
         <f t="shared" si="1"/>
         <v>5.3353138276066719E-6</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0004696579073598E-3</v>
+      </c>
+      <c r="F48" s="1">
+        <f t="shared" si="3"/>
+        <v>4.6965790735974187E-4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>0.11520000000000009</v>
       </c>
@@ -1231,8 +1695,16 @@
         <f t="shared" si="1"/>
         <v>5.3362377155277002E-6</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0004632150794729E-3</v>
+      </c>
+      <c r="F49" s="1">
+        <f t="shared" si="3"/>
+        <v>4.6321507947289024E-4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>0.1168000000000001</v>
       </c>
@@ -1247,8 +1719,16 @@
         <f t="shared" si="1"/>
         <v>5.3383989229230377E-6</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0004570547023051E-3</v>
+      </c>
+      <c r="F50" s="1">
+        <f t="shared" si="3"/>
+        <v>4.5705470230505421E-4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>0.1184000000000001</v>
       </c>
@@ -1263,8 +1743,16 @@
         <f t="shared" si="1"/>
         <v>5.339313369510934E-6</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0004509555210735E-3</v>
+      </c>
+      <c r="F51" s="1">
+        <f t="shared" si="3"/>
+        <v>4.5095552107355822E-4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>0.12000000000000011</v>
       </c>
@@ -1279,8 +1767,16 @@
         <f t="shared" si="1"/>
         <v>5.3391497882252642E-6</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E52" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0004449291490186E-3</v>
+      </c>
+      <c r="F52" s="1">
+        <f t="shared" si="3"/>
+        <v>4.449291490187716E-4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>0.12160000000000011</v>
       </c>
@@ -1295,8 +1791,16 @@
         <f t="shared" si="1"/>
         <v>5.3398965129593939E-6</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E53" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0004391362263946E-3</v>
+      </c>
+      <c r="F53" s="1">
+        <f t="shared" si="3"/>
+        <v>4.391362263946866E-4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>0.12320000000000011</v>
       </c>
@@ -1311,8 +1815,16 @@
         <f t="shared" si="1"/>
         <v>5.3420597740504866E-6</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E54" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0004336087478937E-3</v>
+      </c>
+      <c r="F54" s="1">
+        <f t="shared" si="3"/>
+        <v>4.3360874789370794E-4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>0.12480000000000012</v>
       </c>
@@ -1327,8 +1839,16 @@
         <f t="shared" si="1"/>
         <v>5.3417061716808795E-6</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E55" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0004280213278592E-3</v>
+      </c>
+      <c r="F55" s="1">
+        <f t="shared" si="3"/>
+        <v>4.2802132785904444E-4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>0.12640000000000012</v>
       </c>
@@ -1343,8 +1863,16 @@
         <f t="shared" si="1"/>
         <v>5.3425095026191083E-6</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E56" s="1">
+        <f t="shared" si="2"/>
+        <v>1.00042266689103E-3</v>
+      </c>
+      <c r="F56" s="1">
+        <f t="shared" si="3"/>
+        <v>4.2266689102999234E-4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>0.12800000000000011</v>
       </c>
@@ -1359,8 +1887,16 @@
         <f t="shared" si="1"/>
         <v>5.3440271412120294E-6</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E57" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0004175021204073E-3</v>
+      </c>
+      <c r="F57" s="1">
+        <f t="shared" si="3"/>
+        <v>4.1750212040718936E-4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>0.1296000000000001</v>
       </c>
@@ -1375,8 +1911,16 @@
         <f t="shared" si="1"/>
         <v>5.3446575084981768E-6</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E58" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0004123964126928E-3</v>
+      </c>
+      <c r="F58" s="1">
+        <f t="shared" si="3"/>
+        <v>4.1239641269276021E-4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>0.13120000000000009</v>
       </c>
@@ -1391,8 +1935,16 @@
         <f t="shared" si="1"/>
         <v>5.3457746681945251E-6</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E59" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0004074523375149E-3</v>
+      </c>
+      <c r="F59" s="1">
+        <f t="shared" si="3"/>
+        <v>4.074523375148263E-4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>0.13280000000000008</v>
       </c>
@@ -1407,8 +1959,16 @@
         <f t="shared" si="1"/>
         <v>5.3467462545805228E-6</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E60" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0004026164348327E-3</v>
+      </c>
+      <c r="F60" s="1">
+        <f t="shared" si="3"/>
+        <v>4.026164348328704E-4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>0.13440000000000007</v>
       </c>
@@ -1423,8 +1983,16 @@
         <f t="shared" si="1"/>
         <v>5.3464409094788889E-6</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E61" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0003978006629078E-3</v>
+      </c>
+      <c r="F61" s="1">
+        <f t="shared" si="3"/>
+        <v>3.9780066290765522E-4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>0.13600000000000007</v>
       </c>
@@ -1439,8 +2007,16 @@
         <f t="shared" si="1"/>
         <v>5.3471134314996005E-6</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E62" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0003931701052574E-3</v>
+      </c>
+      <c r="F62" s="1">
+        <f t="shared" si="3"/>
+        <v>3.9317010525732334E-4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>0.13760000000000006</v>
       </c>
@@ -1455,8 +2031,16 @@
         <f t="shared" si="1"/>
         <v>5.3472251065576903E-6</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E63" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0003886064757675E-3</v>
+      </c>
+      <c r="F63" s="1">
+        <f t="shared" si="3"/>
+        <v>3.8860647576727383E-4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>0.13920000000000005</v>
       </c>
@@ -1471,8 +2055,16 @@
         <f t="shared" si="1"/>
         <v>5.3494301000180794E-6</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E64" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0003842981393693E-3</v>
+      </c>
+      <c r="F64" s="1">
+        <f t="shared" si="3"/>
+        <v>3.8429813936911476E-4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>0.14080000000000004</v>
       </c>
@@ -1487,8 +2079,16 @@
         <f t="shared" si="1"/>
         <v>5.3498443112701827E-6</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E65" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0003799605334709E-3</v>
+      </c>
+      <c r="F65" s="1">
+        <f t="shared" si="3"/>
+        <v>3.7996053347089353E-4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>0.14240000000000003</v>
       </c>
@@ -1503,8 +2103,16 @@
         <f t="shared" si="1"/>
         <v>5.3512235904332878E-6</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E66" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0003757881734856E-3</v>
+      </c>
+      <c r="F66" s="1">
+        <f t="shared" si="3"/>
+        <v>3.7578817348548363E-4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>0.14400000000000002</v>
       </c>
@@ -1512,15 +2120,23 @@
         <v>1.4405350615243374E-2</v>
       </c>
       <c r="C67">
-        <f t="shared" ref="C67:C101" si="2">A67*0.1</f>
+        <f t="shared" ref="C67:C101" si="4">A67*0.1</f>
         <v>1.4400000000000003E-2</v>
       </c>
       <c r="D67">
-        <f t="shared" ref="D67:D101" si="3">B67-C67</f>
+        <f t="shared" ref="D67:D101" si="5">B67-C67</f>
         <v>5.3506152433713261E-6</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E67" s="1">
+        <f t="shared" ref="E67:E101" si="6">(B67/100)/A67</f>
+        <v>1.0003715705030119E-3</v>
+      </c>
+      <c r="F67" s="1">
+        <f t="shared" ref="F67:F101" si="7">IF(C67=0, D67, D67/C67)</f>
+        <v>3.7157050301189759E-4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>0.14560000000000001</v>
       </c>
@@ -1528,15 +2144,23 @@
         <v>1.4565352056575996E-2</v>
       </c>
       <c r="C68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4560000000000002E-2</v>
       </c>
       <c r="D68">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3520565759940242E-6</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E68" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003675863032965E-3</v>
+      </c>
+      <c r="F68" s="1">
+        <f t="shared" si="7"/>
+        <v>3.675863032962928E-4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>0.1472</v>
       </c>
@@ -1544,15 +2168,23 @@
         <v>1.4725352637922863E-2</v>
       </c>
       <c r="C69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.472E-2</v>
       </c>
       <c r="D69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3526379228622384E-6</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E69" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003636302936729E-3</v>
+      </c>
+      <c r="F69" s="1">
+        <f t="shared" si="7"/>
+        <v>3.6363029367270642E-4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>0.14879999999999999</v>
       </c>
@@ -1560,15 +2192,23 @@
         <v>1.4885353678316891E-2</v>
       </c>
       <c r="C70">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4879999999999999E-2</v>
       </c>
       <c r="D70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3536783168918467E-6</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E70" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003597902094685E-3</v>
+      </c>
+      <c r="F70" s="1">
+        <f t="shared" si="7"/>
+        <v>3.5979020946853813E-4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>0.15039999999999998</v>
       </c>
@@ -1576,15 +2216,23 @@
         <v>1.5045353987407407E-2</v>
       </c>
       <c r="C71">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5039999999999998E-2</v>
       </c>
       <c r="D71">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3539874074089167E-6</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E71" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003559832052799E-3</v>
+      </c>
+      <c r="F71" s="1">
+        <f t="shared" si="7"/>
+        <v>3.5598320527984822E-4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>0.15199999999999997</v>
       </c>
@@ -1592,15 +2240,23 @@
         <v>1.5205354784474483E-2</v>
       </c>
       <c r="C72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5199999999999998E-2</v>
       </c>
       <c r="D72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.354784474484453E-6</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E72" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003522884522689E-3</v>
+      </c>
+      <c r="F72" s="1">
+        <f t="shared" si="7"/>
+        <v>3.5228845226871404E-4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>0.15359999999999996</v>
       </c>
@@ -1608,15 +2264,23 @@
         <v>1.5365355293261189E-2</v>
       </c>
       <c r="C73">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5359999999999997E-2</v>
       </c>
       <c r="D73">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3552932611916626E-6</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E73" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003486519050255E-3</v>
+      </c>
+      <c r="F73" s="1">
+        <f t="shared" si="7"/>
+        <v>3.4865190502549894E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>0.15519999999999995</v>
       </c>
@@ -1624,15 +2288,23 @@
         <v>1.5525355792200123E-2</v>
       </c>
       <c r="C74">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5519999999999996E-2</v>
       </c>
       <c r="D74">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3557922001269687E-6</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E74" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003450897036164E-3</v>
+      </c>
+      <c r="F74" s="1">
+        <f t="shared" si="7"/>
+        <v>3.450897036164285E-4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>0.15679999999999994</v>
       </c>
@@ -1640,15 +2312,23 @@
         <v>1.5685356563184198E-2</v>
       </c>
       <c r="C75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5679999999999996E-2</v>
       </c>
       <c r="D75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3565631842021622E-6</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E75" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003416175500132E-3</v>
+      </c>
+      <c r="F75" s="1">
+        <f t="shared" si="7"/>
+        <v>3.4161755001289309E-4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>0.15839999999999993</v>
       </c>
@@ -1656,15 +2336,23 @@
         <v>1.5845357767740761E-2</v>
       </c>
       <c r="C76">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5839999999999993E-2</v>
       </c>
       <c r="D76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.357767740767766E-6</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E76" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003382429129273E-3</v>
+      </c>
+      <c r="F76" s="1">
+        <f t="shared" si="7"/>
+        <v>3.3824291292725809E-4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>0.15999999999999992</v>
       </c>
@@ -1672,15 +2360,23 @@
         <v>1.6005357454704435E-2</v>
       </c>
       <c r="C77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5999999999999993E-2</v>
       </c>
       <c r="D77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3574547044417387E-6</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E77" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003348409190278E-3</v>
+      </c>
+      <c r="F77" s="1">
+        <f t="shared" si="7"/>
+        <v>3.3484091902760883E-4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>0.16159999999999991</v>
       </c>
@@ -1688,15 +2384,23 @@
         <v>1.6165358367116703E-2</v>
       </c>
       <c r="C78">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.615999999999999E-2</v>
       </c>
       <c r="D78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3583671167124758E-6</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E78" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003315821235589E-3</v>
+      </c>
+      <c r="F78" s="1">
+        <f t="shared" si="7"/>
+        <v>3.3158212355894056E-4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>0.1631999999999999</v>
       </c>
@@ -1704,15 +2408,23 @@
         <v>1.6325359568166883E-2</v>
       </c>
       <c r="C79">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6319999999999991E-2</v>
       </c>
       <c r="D79">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3595681668919259E-6</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E79" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003284049121871E-3</v>
+      </c>
+      <c r="F79" s="1">
+        <f t="shared" si="7"/>
+        <v>3.2840491218700548E-4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>0.16479999999999989</v>
       </c>
@@ -1720,15 +2432,23 @@
         <v>1.6485360447267196E-2</v>
       </c>
       <c r="C80">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6479999999999991E-2</v>
       </c>
       <c r="D80">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3604472672053038E-6</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E80" s="1">
+        <f t="shared" si="6"/>
+        <v>1.000325269858447E-3</v>
+      </c>
+      <c r="F80" s="1">
+        <f t="shared" si="7"/>
+        <v>3.2526985844692394E-4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>0.16639999999999988</v>
       </c>
@@ -1736,15 +2456,23 @@
         <v>1.6645359628290574E-2</v>
       </c>
       <c r="C81">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6639999999999988E-2</v>
       </c>
       <c r="D81">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3596282905861437E-6</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E81" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003220930463093E-3</v>
+      </c>
+      <c r="F81" s="1">
+        <f t="shared" si="7"/>
+        <v>3.2209304630926368E-4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>0.16799999999999987</v>
       </c>
@@ -1752,15 +2480,23 @@
         <v>1.6805360465333066E-2</v>
       </c>
       <c r="C82">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6799999999999989E-2</v>
       </c>
       <c r="D82">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3604653330770191E-6</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E82" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003190753174452E-3</v>
+      </c>
+      <c r="F82" s="1">
+        <f t="shared" si="7"/>
+        <v>3.190753174450609E-4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>0.16959999999999986</v>
       </c>
@@ -1768,15 +2504,23 @@
         <v>1.6965361595957604E-2</v>
       </c>
       <c r="C83">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6959999999999986E-2</v>
       </c>
       <c r="D83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3615959576189254E-6</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E83" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003161318371237E-3</v>
+      </c>
+      <c r="F83" s="1">
+        <f t="shared" si="7"/>
+        <v>3.1613183712375767E-4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>0.17119999999999985</v>
       </c>
@@ -1784,15 +2528,23 @@
         <v>1.7125361664493934E-2</v>
       </c>
       <c r="C84">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.7119999999999986E-2</v>
       </c>
       <c r="D84">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3616644939483149E-6</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E84" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003131813372632E-3</v>
+      </c>
+      <c r="F84" s="1">
+        <f t="shared" si="7"/>
+        <v>3.1318133726333639E-4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>0.17279999999999984</v>
       </c>
@@ -1800,15 +2552,23 @@
         <v>1.7285363115311911E-2</v>
       </c>
       <c r="C85">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.7279999999999986E-2</v>
       </c>
       <c r="D85">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3631153119244879E-6</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E85" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003103654694402E-3</v>
+      </c>
+      <c r="F85" s="1">
+        <f t="shared" si="7"/>
+        <v>3.1036546944007476E-4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>0.17439999999999983</v>
       </c>
@@ -1816,15 +2576,23 @@
         <v>1.7445363545095096E-2</v>
       </c>
       <c r="C86">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.7439999999999983E-2</v>
       </c>
       <c r="D86">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3635450951126928E-6</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E86" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003075427233437E-3</v>
+      </c>
+      <c r="F86" s="1">
+        <f t="shared" si="7"/>
+        <v>3.0754272334361803E-4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>0.17599999999999982</v>
       </c>
@@ -1832,15 +2600,23 @@
         <v>1.7605363463423285E-2</v>
       </c>
       <c r="C87">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.7599999999999984E-2</v>
       </c>
       <c r="D87">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3634634233010181E-6</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E87" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003047422399603E-3</v>
+      </c>
+      <c r="F87" s="1">
+        <f t="shared" si="7"/>
+        <v>3.0474223996028541E-4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>0.17759999999999981</v>
       </c>
@@ -1848,15 +2624,23 @@
         <v>1.7765365329580052E-2</v>
       </c>
       <c r="C88">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.7759999999999981E-2</v>
       </c>
       <c r="D88">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3653295800717982E-6</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E88" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0003021018907697E-3</v>
+      </c>
+      <c r="F88" s="1">
+        <f t="shared" si="7"/>
+        <v>3.0210189076980876E-4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>0.1791999999999998</v>
       </c>
@@ -1864,15 +2648,23 @@
         <v>1.7925365231250472E-2</v>
       </c>
       <c r="C89">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.7919999999999981E-2</v>
       </c>
       <c r="D89">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3652312504912092E-6</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E89" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0002993990653175E-3</v>
+      </c>
+      <c r="F89" s="1">
+        <f t="shared" si="7"/>
+        <v>2.9939906531759009E-4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>0.18079999999999979</v>
       </c>
@@ -1880,15 +2672,23 @@
         <v>1.8085366692327971E-2</v>
       </c>
       <c r="C90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.8079999999999982E-2</v>
       </c>
       <c r="D90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3666923279897805E-6</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E90" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0002968303278756E-3</v>
+      </c>
+      <c r="F90" s="1">
+        <f t="shared" si="7"/>
+        <v>2.9683032787554127E-4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>0.18239999999999978</v>
       </c>
@@ -1896,15 +2696,23 @@
         <v>1.8245365661237311E-2</v>
       </c>
       <c r="C91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.8239999999999978E-2</v>
       </c>
       <c r="D91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3656612373324808E-6</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E91" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0002941700239765E-3</v>
+      </c>
+      <c r="F91" s="1">
+        <f t="shared" si="7"/>
+        <v>2.941700239765618E-4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>0.18399999999999977</v>
       </c>
@@ -1912,15 +2720,23 @@
         <v>1.8405367667835883E-2</v>
       </c>
       <c r="C92">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.8399999999999979E-2</v>
       </c>
       <c r="D92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.367667835903811E-6</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E92" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0002917210780384E-3</v>
+      </c>
+      <c r="F92" s="1">
+        <f t="shared" si="7"/>
+        <v>2.9172107803825093E-4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>0.18559999999999977</v>
       </c>
@@ -1928,15 +2744,23 @@
         <v>1.8565367465479956E-2</v>
       </c>
       <c r="C93">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.8559999999999976E-2</v>
       </c>
       <c r="D93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3674654799801269E-6</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E93" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0002891953383611E-3</v>
+      </c>
+      <c r="F93" s="1">
+        <f t="shared" si="7"/>
+        <v>2.8919533836099857E-4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>0.18719999999999976</v>
       </c>
@@ -1944,15 +2768,23 @@
         <v>1.8725368665729915E-2</v>
       </c>
       <c r="C94">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.8719999999999976E-2</v>
       </c>
       <c r="D94">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3686657299385765E-6</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E94" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0002867876992489E-3</v>
+      </c>
+      <c r="F94" s="1">
+        <f t="shared" si="7"/>
+        <v>2.8678769924885597E-4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>0.18879999999999975</v>
       </c>
@@ -1960,15 +2792,23 @@
         <v>1.888536914801801E-2</v>
       </c>
       <c r="C95">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.8879999999999977E-2</v>
       </c>
       <c r="D95">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3691480180334539E-6</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E95" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0002843828399383E-3</v>
+      </c>
+      <c r="F95" s="1">
+        <f t="shared" si="7"/>
+        <v>2.8438283993821296E-4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>0.19039999999999974</v>
       </c>
@@ -1976,15 +2816,23 @@
         <v>1.9045369162019064E-2</v>
       </c>
       <c r="C96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9039999999999974E-2</v>
       </c>
       <c r="D96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3691620190907119E-6</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E96" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0002819938035236E-3</v>
+      </c>
+      <c r="F96" s="1">
+        <f t="shared" si="7"/>
+        <v>2.8199380352367221E-4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>0.19199999999999973</v>
       </c>
@@ -1992,15 +2840,23 @@
         <v>1.9205371116147077E-2</v>
       </c>
       <c r="C97">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9199999999999974E-2</v>
       </c>
       <c r="D97">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3711161471028945E-6</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E97" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0002797456326617E-3</v>
+      </c>
+      <c r="F97" s="1">
+        <f t="shared" si="7"/>
+        <v>2.7974563266160949E-4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>0.19359999999999972</v>
       </c>
@@ -2008,15 +2864,23 @@
         <v>1.9365371869839523E-2</v>
       </c>
       <c r="C98">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9359999999999974E-2</v>
       </c>
       <c r="D98">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3718698395481546E-6</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E98" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0002774726156792E-3</v>
+      </c>
+      <c r="F98" s="1">
+        <f t="shared" si="7"/>
+        <v>2.7747261567914061E-4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>0.19519999999999971</v>
       </c>
@@ -2024,15 +2888,23 @@
         <v>1.9525372350247549E-2</v>
       </c>
       <c r="C99">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9519999999999971E-2</v>
       </c>
       <c r="D99">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3723502475774843E-6</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E99" s="1">
+        <f t="shared" si="6"/>
+        <v>1.000275222861044E-3</v>
+      </c>
+      <c r="F99" s="1">
+        <f t="shared" si="7"/>
+        <v>2.7522286104392891E-4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>0.1967999999999997</v>
       </c>
@@ -2040,15 +2912,23 @@
         <v>1.9685371741170583E-2</v>
       </c>
       <c r="C100">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9679999999999972E-2</v>
       </c>
       <c r="D100">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3717411706115381E-6</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E100" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0002729543277752E-3</v>
+      </c>
+      <c r="F100" s="1">
+        <f t="shared" si="7"/>
+        <v>2.7295432777497692E-4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>0.19839999999999969</v>
       </c>
@@ -2056,12 +2936,20 @@
         <v>1.984537205554128E-2</v>
       </c>
       <c r="C101">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9839999999999969E-2</v>
       </c>
       <c r="D101">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3720555413111493E-6</v>
+      </c>
+      <c r="E101" s="1">
+        <f t="shared" si="6"/>
+        <v>1.0002707689284935E-3</v>
+      </c>
+      <c r="F101" s="1">
+        <f t="shared" si="7"/>
+        <v>2.7076892849350594E-4</v>
       </c>
     </row>
   </sheetData>

--- a/Homework2/my-simulation/question9.xlsx
+++ b/Homework2/my-simulation/question9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Document_forme\project_tiny\Cource_report\DTUD\Homework2\my-simulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9A8538-5364-4B1F-8CB6-8193FF6D166D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBD25E9-9433-4A70-9A7C-8BE9D6477551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F11CDC6A-F5E9-4EBC-949A-D08DA2F43347}"/>
   </bookViews>
@@ -508,11 +508,11 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D2">
-        <f>B2-C2</f>
+        <f>ABS(B2-C2)</f>
         <v>5.212711219392506E-6</v>
       </c>
       <c r="E2" s="1">
-        <f>(B2/100)/A2</f>
+        <f>ABS(B2/100)/A2</f>
         <v>1.0013031778048481E-3</v>
       </c>
       <c r="F2" s="1">
@@ -539,11 +539,11 @@
         <v>4.1599999999999996E-3</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D66" si="1">B3-C3</f>
+        <f t="shared" ref="D3:D66" si="1">ABS(B3-C3)</f>
         <v>5.2193972622793794E-6</v>
       </c>
       <c r="E3" s="1">
-        <f t="shared" ref="E3:E66" si="2">(B3/100)/A3</f>
+        <f t="shared" ref="E3:E66" si="2">ABS(B3/100)/A3</f>
         <v>1.0012546628034324E-3</v>
       </c>
       <c r="F3" s="1">
@@ -2124,11 +2124,11 @@
         <v>1.4400000000000003E-2</v>
       </c>
       <c r="D67">
-        <f t="shared" ref="D67:D101" si="5">B67-C67</f>
+        <f t="shared" ref="D67:D101" si="5">ABS(B67-C67)</f>
         <v>5.3506152433713261E-6</v>
       </c>
       <c r="E67" s="1">
-        <f t="shared" ref="E67:E101" si="6">(B67/100)/A67</f>
+        <f t="shared" ref="E67:E101" si="6">ABS(B67/100)/A67</f>
         <v>1.0003715705030119E-3</v>
       </c>
       <c r="F67" s="1">
